--- a/resources/templates/standard/M4100-04.xlsx
+++ b/resources/templates/standard/M4100-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>3정 5행 지적 및 시정 대책서</t>
   </si>
@@ -637,13 +640,15 @@
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -661,20 +666,20 @@
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
@@ -849,7 +854,7 @@
     <row r="4" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -867,7 +872,7 @@
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
@@ -920,7 +925,7 @@
     <row r="5" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -938,7 +943,7 @@
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
@@ -991,7 +996,7 @@
     <row r="6" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1009,7 +1014,7 @@
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
       <c r="R6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
@@ -1062,7 +1067,7 @@
     <row r="7" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1131,7 +1136,7 @@
     <row r="8" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -1200,7 +1205,7 @@
     <row r="9" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -1213,7 +1218,7 @@
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
@@ -1271,7 +1276,7 @@
     <row r="10" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -2144,7 +2149,7 @@
     <row r="23" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -2157,7 +2162,7 @@
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
       <c r="M23" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N23" s="19"/>
       <c r="O23" s="19"/>
@@ -2215,7 +2220,7 @@
     <row r="24" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
